--- a/data/trans_camb/P20B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 16,0</t>
+          <t>-11,91; 16,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 19,21</t>
+          <t>-12,13; 19,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 22,41</t>
+          <t>-7,01; 22,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 9,68</t>
+          <t>-15,43; 9,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 19,36</t>
+          <t>-8,94; 19,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 4,18</t>
+          <t>-20,43; 4,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 9,06</t>
+          <t>-10,21; 8,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 16,03</t>
+          <t>-6,18; 15,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 9,43</t>
+          <t>-9,76; 9,47</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 85,76</t>
+          <t>-35,17; 88,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 106,01</t>
+          <t>-38,64; 101,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 117,86</t>
+          <t>-22,3; 136,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 38,85</t>
+          <t>-39,98; 36,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 78,2</t>
+          <t>-24,29; 78,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 17,1</t>
+          <t>-54,39; 17,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 38,16</t>
+          <t>-29,83; 33,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 66,62</t>
+          <t>-18,29; 64,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 38,35</t>
+          <t>-28,65; 38,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 24,7</t>
+          <t>-4,84; 24,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 36,46</t>
+          <t>3,84; 37,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 27,17</t>
+          <t>-2,76; 27,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 17,02</t>
+          <t>0,03; 17,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 21,54</t>
+          <t>2,36; 21,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 22,08</t>
+          <t>2,06; 21,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 17,68</t>
+          <t>2,85; 17,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 23,33</t>
+          <t>7,16; 23,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 22,45</t>
+          <t>5,72; 22,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 204,01</t>
+          <t>-16,53; 214,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 298,06</t>
+          <t>10,55; 314,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 236,44</t>
+          <t>-9,07; 240,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 213,21</t>
+          <t>-3,32; 226,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 257,35</t>
+          <t>10,57; 292,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 257,96</t>
+          <t>6,29; 266,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 159,18</t>
+          <t>13,58; 169,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,78; 203,06</t>
+          <t>37,51; 218,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 201,42</t>
+          <t>25,57; 212,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 29,88</t>
+          <t>-42,74; 30,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 5,19</t>
+          <t>-48,26; 6,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 19,94</t>
+          <t>-35,97; 17,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 26,23</t>
+          <t>-6,66; 27,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 2,5</t>
+          <t>-22,79; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 17,64</t>
+          <t>-10,16; 18,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 18,27</t>
+          <t>-16,34; 17,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -1,2</t>
+          <t>-26,42; 0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 14,26</t>
+          <t>-15,12; 14,47</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,14</t>
+          <t>-100,0; 221,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,24; 31,13</t>
+          <t>-91,14; 33,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 93,21</t>
+          <t>-67,49; 108,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 555,04</t>
+          <t>-47,15; 727,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 455,52</t>
+          <t>-48,55; 554,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 137,63</t>
+          <t>-59,39; 121,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,29; 0,7</t>
+          <t>-87,44; 14,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 100,41</t>
+          <t>-47,68; 105,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 14,25</t>
+          <t>-6,14; 13,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 17,68</t>
+          <t>-3,07; 17,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 17,17</t>
+          <t>-3,26; 16,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 11,25</t>
+          <t>-2,65; 11,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,06</t>
+          <t>-3,43; 12,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 9,43</t>
+          <t>-4,1; 9,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 9,5</t>
+          <t>-1,25; 9,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,73</t>
+          <t>-0,33; 11,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 11,19</t>
+          <t>-0,23; 11,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 69,47</t>
+          <t>-19,52; 66,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 80,31</t>
+          <t>-9,57; 86,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 87,12</t>
+          <t>-10,45; 81,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 71,67</t>
+          <t>-11,54; 68,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 67,62</t>
+          <t>-15,11; 75,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 54,15</t>
+          <t>-17,34; 61,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 49,12</t>
+          <t>-5,43; 51,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 60,56</t>
+          <t>-0,99; 61,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 58,05</t>
+          <t>-0,94; 58,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 16,06</t>
+          <t>-11,56; 15,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 19,3</t>
+          <t>-11,78; 20,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 22,61</t>
+          <t>-7,62; 22,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 9,1</t>
+          <t>-14,59; 9,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 19,81</t>
+          <t>-8,76; 20,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 4,52</t>
+          <t>-19,78; 6,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 8,27</t>
+          <t>-10,0; 8,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 15,49</t>
+          <t>-6,52; 15,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 9,47</t>
+          <t>-10,81; 9,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,83%</t>
+          <t>-20,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,83%</t>
+          <t>-0,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 88,39</t>
+          <t>-35,24; 83,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 101,17</t>
+          <t>-38,01; 110,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 136,08</t>
+          <t>-23,48; 116,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 36,63</t>
+          <t>-38,04; 42,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 78,86</t>
+          <t>-24,55; 82,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 17,19</t>
+          <t>-51,29; 25,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 33,97</t>
+          <t>-29,85; 35,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 64,3</t>
+          <t>-17,97; 61,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 38,45</t>
+          <t>-31,09; 40,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>11,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 24,9</t>
+          <t>-6,17; 24,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 37,22</t>
+          <t>2,79; 35,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 27,48</t>
+          <t>-1,93; 28,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 17,98</t>
+          <t>0,47; 18,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,9</t>
+          <t>2,12; 20,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 21,91</t>
+          <t>2,21; 21,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 17,96</t>
+          <t>2,74; 18,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 23,49</t>
+          <t>7,24; 23,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 22,93</t>
+          <t>5,94; 22,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 214,07</t>
+          <t>-19,38; 200,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 314,96</t>
+          <t>8,9; 318,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 240,09</t>
+          <t>-6,89; 253,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 226,85</t>
+          <t>-0,75; 210,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 292,34</t>
+          <t>10,3; 246,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 266,4</t>
+          <t>9,17; 259,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 169,64</t>
+          <t>13,26; 176,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 218,1</t>
+          <t>36,98; 218,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,57; 212,21</t>
+          <t>27,77; 216,15</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,68</t>
+          <t>-9,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 30,92</t>
+          <t>-43,38; 27,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 6,19</t>
+          <t>-44,81; 7,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 17,57</t>
+          <t>-36,54; 16,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 27,35</t>
+          <t>-8,97; 24,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 3,31</t>
+          <t>-23,76; 3,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 18,09</t>
+          <t>-9,45; 20,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 17,01</t>
+          <t>-15,86; 16,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 0,25</t>
+          <t>-26,34; -0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 14,47</t>
+          <t>-14,48; 14,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,97%</t>
+          <t>-24,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,59</t>
+          <t>-100,0; 257,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,14; 33,01</t>
+          <t>-89,34; 46,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 108,39</t>
+          <t>-66,67; 80,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 727,34</t>
+          <t>-50,08; 537,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 554,58</t>
+          <t>-46,91; 537,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 121,37</t>
+          <t>-56,11; 111,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,44; 14,32</t>
+          <t>-87,82; 9,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 105,71</t>
+          <t>-47,51; 114,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 13,46</t>
+          <t>-6,96; 12,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,54</t>
+          <t>-2,92; 18,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 16,04</t>
+          <t>-3,21; 16,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 11,62</t>
+          <t>-2,61; 11,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,17</t>
+          <t>-3,2; 12,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 9,41</t>
+          <t>-3,83; 9,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,86</t>
+          <t>-1,14; 9,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,75</t>
+          <t>-0,07; 12,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 11,09</t>
+          <t>-0,08; 11,8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 66,68</t>
+          <t>-21,79; 59,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 86,94</t>
+          <t>-11,49; 83,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 81,6</t>
+          <t>-10,05; 81,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 68,51</t>
+          <t>-11,73; 70,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,03</t>
+          <t>-14,13; 72,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 61,3</t>
+          <t>-17,98; 59,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 51,18</t>
+          <t>-4,15; 51,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 61,44</t>
+          <t>-0,56; 63,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 58,42</t>
+          <t>-0,59; 60,45</t>
         </is>
       </c>
     </row>
